--- a/docs/现行穿搭规则一览.xlsx
+++ b/docs/现行穿搭规则一览.xlsx
@@ -546,7 +546,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>这一步现在没做。发给 AI 的是当前用户衣橱里的全部衣服，厚的薄的都在名单里。冷热门槛是 AI 出套之后才补拦。</t>
+          <t>先筛现在会做：按天气冷热、硬性需求（颜色/厚薄）、排除品类从整橱筛出候选衣橱，再交给 AI。没有指定核心时不造核心。筛完没衣服则 0 套。</t>
         </is>
       </c>
     </row>
@@ -558,7 +558,7 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>模型只能用名单里的真实衣服 ID，写出最多 3 套和理由。提示要求：必须带核心、整套 ID 不能完全重复。审美组合和措辞靠模型，不是本地公式。</t>
+          <t>模型只能用候选衣橱里的真实衣服 ID，写出最多 3 套和理由。有核心才必须带上；没核心不必共用一件。整套是否相同只看衣服 ID 集合。</t>
         </is>
       </c>
     </row>
@@ -606,7 +606,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>同一套里同一件出现两次只留一次；三套衣服 ID 完全一样只留一套；最多留 3 套；补温度提醒、颜色关系那句话。不再补待洗/收纳等状态提醒。</t>
+          <t>同一套里同一件出现两次只留一次；两套衣服 ID 完全一样只留一套；最多留 3 套；指定了核心却没带上则加回去；补需求冲突提醒、温度提醒、颜色关系那句话。</t>
         </is>
       </c>
     </row>
@@ -630,7 +630,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>小程序里 AI 失败会交回空结果。页面这时才改用「组套规则」那三套（方案A/B/C）。AI 一出套，组套规则就算过了，你看不见。</t>
+          <t>AI 失败或交回 0 套时，小程序不再本地组套，直接没有搭配。</t>
         </is>
       </c>
     </row>
@@ -642,7 +642,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>AI 交回至少 1 套 → 只展示 AI 结果。AI 交回 0 套 → 展示本地组套结果。</t>
+          <t>AI 交回至少 1 套 → 展示这些套。否则空白。</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>没做前筛 → AI 组了三套 → 后核只拦了 ID/核心/冷热。所以两条黑裙子能出现在第 3 套里。</t>
+          <t>没指定核心时先筛再组套，三套不必围着最新一件。</t>
         </is>
       </c>
     </row>
@@ -666,7 +666,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>对应那句话：先筛 → AI 组套 → 后核；AI 不可用时才走组套。整理日期：2026-08-22。待洗、收纳、可穿等库存状态已废除。</t>
+          <t>对应：先筛候选衣橱 → AI 组套 → 后核。AI 不可用时不出套。整理日期：2026-08-22。</t>
         </is>
       </c>
     </row>
@@ -741,12 +741,12 @@
     <row r="5" ht="48" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>核心 · 系统默认</t>
+          <t>核心 · 系统默认（已废除）</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>没指定时：拿最新一件当核心。排序按衣服 ID 从大到小。不再按可穿/待洗分叉。</t>
+          <t>没指定时：本次不存在核心衣物。不得拿最新一件或合格池里任意一件当默认核心。</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>只有 AI 交回 0 套时，页面才展示这套组套结果。本地其实每次都会先算一遍，但 AI 有结果就被丢掉不给用户看。</t>
+          <t>小程序已废除本地组套兜底。本表只描述网页旧模式仍可能走的互补品类打分，用户产品不再展示。</t>
         </is>
       </c>
     </row>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>设计写的是先丢掉明显冷热不对的非核心再给 AI。代码把全部衣服都给了 AI，冷热只在出套后补拦。</t>
+          <t>前筛已做：候选衣橱先硬筛再给 AI。冷热、硬性需求、排除品类在送给模型之前就会丢掉不合格衣服。</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>小程序不再按待洗/收纳筛衣或提醒。网页旧模式仍可能只从可穿里挑，见上一行。</t>
+          <t>本地组套兜底已废除。AI 不可用时小程序直接 0 套，不再用方案A/B/C 顶上。</t>
         </is>
       </c>
     </row>
@@ -1554,7 +1554,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>本表只记当前事实，不是改法。小程序 AI 搭配不走 wardrobe-query-parser。小程序已废除库存状态。整理日期：2026-08-22。</t>
+          <t>本表只记当前事实。小程序 AI 搭配已接上排除品类（不要裙子不含裤子）。整理日期：2026-08-22。</t>
         </is>
       </c>
     </row>
